--- a/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00990A(新納入)、00400A(129,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-322,000)、00400A(-28,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(85,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00981A(-322,000)、00400A(-28,000)</t>
+          <t>00400A(-48,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,45 +644,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00981A(85,000)</t>
+          <t>00981A(100,000)、00403A(80,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>00400A(-48,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00981A(100,000)、00403A(80,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00991A(109,000)、00403A(92,000)、00400A(20,000)</t>
+          <t>00990A(新納入)、00400A(129,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,42 +481,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00991A(70,000)</t>
+          <t>00403A(92,000)、00400A(20,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-800,000)、00400A(-140,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -534,127 +534,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00991A(-649,000)、00400A(-194,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00981A(364,000)、00400A(60,000)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00981A(-322,000)、00400A(-28,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00981A(85,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00400A(-48,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00981A(100,000)、00403A(80,000)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>00403A(-800,000)、00400A(-140,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00990A(新納入)、00400A(129,000)</t>
+          <t>00981A(1,682,000)、00990A(新納入)、00407A(123,000)、00993A(新納入)、00400A(356,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,60 +481,540 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00403A(92,000)、00400A(20,000)</t>
+          <t>00991A(70,000)、00993A(8,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(-800,000)、00400A(-140,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>00981A(67,000)、00403A(15,000)、00990A(新納入)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00407A(-15,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00981A(220,000)、00403A(80,000)、00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>00407A(-145,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00991A(-649,000)、00990A(-213,000)、00400A(-194,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00981A(364,000)、00400A(60,000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>00993A(-8,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00993A(7,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>00981A(-322,000)、00400A(-28,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00991A(129,000)、00403A(92,000)、00400A(20,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(76,000)、00403A(80,000)、00993A(5,000)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00403A(-800,000)、00400A(-140,000)</t>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00407A(-10,000)、00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00400A(2,096,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>00403A(-5,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00403A(400,000)、00993A(4,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>00403A(-950,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00981A(85,000)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>00400A(-48,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00993A(2,000)、00400A(253,000)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00981A(1,256,000)、00993A(5,000)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00981A(29,000)、00403A(28,000)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00993A(4,000)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>00400A(-301,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>00981A(-1,034,000)、00993A(-96,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(1,682,000)、00990A(新納入)、00407A(123,000)、00993A(新納入)、00400A(356,000)</t>
+          <t>00981A(1,682,000)、00985A(105,000)、00990A(新納入)、00407A(123,000)、00993A(新納入)、00400A(356,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,16 +481,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,28 +499,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00991A(70,000)、00993A(8,000)</t>
+          <t>00981A(364,000)、00985A(304,000)、00992A(50,000)、00400A(60,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-800,000)、00400A(-140,000)</t>
+          <t>00993A(-8,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -529,28 +529,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00981A(67,000)、00403A(15,000)、00990A(新納入)</t>
+          <t>00991A(129,000)、00403A(92,000)、00992A(30,000)、00400A(20,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00407A(-15,000)</t>
+          <t>00985A(-15,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,58 +559,58 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00981A(220,000)、00403A(80,000)、00993A(新納入)</t>
+          <t>00991A(70,000)、00993A(8,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00407A(-145,000)</t>
+          <t>00403A(-800,000)、00985A(-28,000)、00400A(-140,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(67,000)、00403A(15,000)、00992A(8,000)、00990A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00991A(-649,000)、00990A(-213,000)、00400A(-194,000)</t>
+          <t>00407A(-15,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -619,28 +619,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00981A(364,000)、00400A(60,000)</t>
+          <t>00981A(220,000)、00403A(80,000)、00992A(33,000)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00993A(-8,000)</t>
+          <t>00407A(-145,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -649,118 +649,118 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00993A(7,000)</t>
+          <t>00985A(14,000)、00992A(7,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00981A(-322,000)、00400A(-28,000)</t>
+          <t>00407A(-10,000)、00993A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00991A(129,000)、00403A(92,000)、00400A(20,000)</t>
+          <t>00985A(102,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-649,000)、00990A(-213,000)、00400A(-194,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00981A(76,000)、00403A(80,000)、00993A(5,000)</t>
+          <t>00985A(57,000)、00993A(7,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-322,000)、00400A(-28,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(85,000)、00985A(19,000)、00992A(27,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00407A(-10,000)、00993A(-1,000)</t>
+          <t>00400A(-48,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -769,28 +769,28 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00400A(2,096,000)</t>
+          <t>00992A(144,000)、00993A(4,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00403A(-5,000,000)</t>
+          <t>00985A(-127,000)、00400A(-301,000)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>00403A(400,000)、00993A(4,000)</t>
+          <t>00981A(76,000)、00403A(80,000)、00992A(50,000)、00993A(5,000)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -811,16 +811,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -829,84 +829,84 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00993A(新納入)</t>
+          <t>00400A(2,096,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>00403A(-950,000)</t>
+          <t>00403A(-5,000,000)、00985A(-1,396,000)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00981A(85,000)</t>
+          <t>00985A(35,000)、00992A(5,000)、00993A(3,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>00400A(-48,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00993A(2,000)、00400A(253,000)</t>
+          <t>00985A(20,000)、00992A(35,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00400A(-22,000)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00981A(1,256,000)、00993A(5,000)</t>
+          <t>00992A(18,000)、00993A(5,000)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>00981A(29,000)、00403A(28,000)</t>
+          <t>00403A(400,000)、00993A(4,000)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -979,42 +979,582 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>00993A(4,000)</t>
+          <t>00400A(239,000)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>00400A(-301,000)</t>
+          <t>00985A(-6,000)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>00985A(77,000)、00992A(28,000)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>00992A(2,000)、00993A(2,000)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>00985A(260,000)、00992A(14,000)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>00985A(1,575,000)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>00982A(-1,672,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>00992A(8,000)、00993A(2,000)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>00985A(967,000)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>00407A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>00985A(30,000)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>00993A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>00403A(-950,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>00985A(406,000)、00400A(702,000)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>00993A(2,000)、00400A(253,000)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>00985A(210,000)、00993A(10,000)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>00981A(1,256,000)、00993A(5,000)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>00985A(55,000)、00993A(2,000)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>00992A(500,000)、00993A(4,000)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>00992A(200,000)、00993A(16,000)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>00981A(29,000)、00403A(28,000)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>00985A(143,000)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>00403A(-400,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>6669</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>00981A(-1,034,000)、00993A(-96,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>00985A(6,000)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>00403A(全數賣出)</t>
         </is>
       </c>
     </row>
